--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8E2CD0-48F4-4095-A2C2-7DB5DCED4410}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF235D2-2AFA-44A8-97DB-F4EB3B89E443}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="37">
   <si>
     <t>Date</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>SIP (DRAFT)</t>
+  </si>
+  <si>
+    <t>414-B</t>
   </si>
 </sst>
 </file>
@@ -2390,8 +2393,8 @@
       <c r="G68" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="7">
-        <v>301</v>
+      <c r="H68" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="I68" s="8"/>
     </row>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF235D2-2AFA-44A8-97DB-F4EB3B89E443}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64639EE4-0323-4BB7-9F08-3AE9B6526D88}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="3300" yWindow="3300" windowWidth="19200" windowHeight="11170" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -149,12 +149,48 @@
   <si>
     <t>414-B</t>
   </si>
+  <si>
+    <t>BRM</t>
+  </si>
+  <si>
+    <t>NEK</t>
+  </si>
+  <si>
+    <t>BFFFS</t>
+  </si>
+  <si>
+    <t>CKS</t>
+  </si>
+  <si>
+    <t>SCN</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>Parichay</t>
+  </si>
+  <si>
+    <t>Parichay 2026 </t>
+  </si>
+  <si>
+    <t>SIP</t>
+  </si>
+  <si>
+    <t>Area - SED</t>
+  </si>
+  <si>
+    <t>MBT</t>
+  </si>
+  <si>
+    <t>Master Thesis</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +247,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,6 +298,18 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -277,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -322,6 +383,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -660,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B20C511-92BA-4145-A0DE-1431FC38FEF8}">
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -2964,6 +3064,2498 @@
         <v>301</v>
       </c>
       <c r="I89" s="10"/>
+    </row>
+    <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A90" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H90" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A91" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H91" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A92" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B92" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G92" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A93" s="16">
+        <v>46282</v>
+      </c>
+      <c r="B93" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G93" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H93" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A94" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B94" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H94" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A95" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H95" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+      <c r="A96" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H96" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A97" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B97" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H97" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A98" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H98" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A99" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H99" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A100" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G100" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H100" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A101" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H101" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A102" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H102" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A103" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G103" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H103" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A104" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H104" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A105" s="16">
+        <v>46287</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F105" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H105" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A106" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G106" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H106" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A107" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H107" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A108" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F108" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H108" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A109" s="16">
+        <v>46288</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F109" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H109" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A110" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G110" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H110" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A111" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G111" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H111" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A112" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G112" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H112" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A113" s="16">
+        <v>46289</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F113" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G113" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H113" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A114" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G114" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H114" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A115" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G115" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H115" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A116" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F116" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G116" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H116" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A117" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F117" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G117" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H117" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A118" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G118" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H118" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A119" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H119" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A120" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F120" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G120" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H120" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A121" s="16">
+        <v>46291</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F121" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G121" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H121" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A122" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G122" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H122" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A123" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G123" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A124" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F124" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G124" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H124" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A125" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F125" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G125" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H125" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A126" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H126" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A127" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G127" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H127" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A128" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F128" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G128" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H128" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A129" s="16">
+        <v>46294</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F129" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="G129" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H129" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A130" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H130" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A131" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G131" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H131" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A132" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F132" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G132" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H132" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A133" s="16">
+        <v>46295</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F133" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G133" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H133" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A134" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G134" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H134" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A135" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B135" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G135" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H135" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A136" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F136" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G136" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H136" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A137" s="16">
+        <v>46296</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F137" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G137" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H137" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A138" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G138" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H138" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A139" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G139" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H139" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A140" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F140" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G140" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H140" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A141" s="16">
+        <v>46298</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F141" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G141" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H141" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A142" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H142" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A143" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F143" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G143" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H143" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A144" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F144" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G144" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H144" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A145" s="16">
+        <v>46300</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F145" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G145" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H145" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A146" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C146" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G146" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H146" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A147" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H147" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A148" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C148" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F148" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G148" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H148" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A149" s="16">
+        <v>46301</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C149" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F149" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G149" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H149" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A150" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G150" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H150" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A151" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F151" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G151" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H151" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A152" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F152" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G152" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="H152" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A153" s="16">
+        <v>46302</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F153" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G153" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H153" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A154" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G154" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H154" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A155" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D155" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F155" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G155" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H155" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A156" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F156" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G156" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H156" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A157" s="16">
+        <v>46303</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F157" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G157" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H157" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A158" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B158" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C158" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D158" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G158" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H158" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A159" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C159" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D159" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G159" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H159" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A160" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D160" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F160" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G160" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H160" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A161" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C161" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F161" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G161" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H161" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A162" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D162" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G162" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H162" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A163" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B163" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D163" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F163" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G163" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H163" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A164" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F164" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G164" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H164" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A165" s="16">
+        <v>46307</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D165" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F165" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G165" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H165" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A166" s="16">
+        <v>46308</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D166" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G166" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H166" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A167" s="16">
+        <v>46308</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F167" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G167" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H167" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A168" s="16">
+        <v>46308</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D168" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F168" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G168" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H168" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A169" s="16">
+        <v>46308</v>
+      </c>
+      <c r="B169" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D169" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F169" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G169" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H169" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A170" s="16">
+        <v>46309</v>
+      </c>
+      <c r="B170" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G170" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H170" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A171" s="16">
+        <v>46309</v>
+      </c>
+      <c r="B171" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F171" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G171" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H171" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A172" s="16">
+        <v>46309</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D172" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F172" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G172" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H172" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A173" s="16">
+        <v>46309</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F173" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G173" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H173" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A174" s="16">
+        <v>46310</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D174" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G174" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H174" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A175" s="16">
+        <v>46310</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F175" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G175" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H175" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A176" s="16">
+        <v>46310</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C176" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F176" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G176" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H176" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A177" s="16">
+        <v>46310</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F177" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G177" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H177" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A178" s="16">
+        <v>46311</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C178" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D178" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G178" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H178" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A179" s="16">
+        <v>46311</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D179" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F179" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G179" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H179" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A180" s="16">
+        <v>46311</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D180" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F180" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G180" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="H180" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A181" s="16">
+        <v>46311</v>
+      </c>
+      <c r="B181" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D181" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F181" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G181" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H181" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A182" s="16">
+        <v>46312</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D182" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" s="20"/>
+      <c r="G182" s="20"/>
+      <c r="H182" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A183" s="16">
+        <v>46312</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D183" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H183" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A184" s="16">
+        <v>46312</v>
+      </c>
+      <c r="B184" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C184" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D184" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F184" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G184" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H184" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A185" s="16">
+        <v>46312</v>
+      </c>
+      <c r="B185" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C185" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D185" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F185" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G185" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H185" s="22">
+        <v>301</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64639EE4-0323-4BB7-9F08-3AE9B6526D88}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFE3DE5-6A4C-47D6-9236-4E9FBEAC05E6}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="3300" windowWidth="19200" windowHeight="11170" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -4729,7 +4729,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A154" s="16">
         <v>46303</v>
       </c>
@@ -4746,16 +4746,16 @@
         <v>12</v>
       </c>
       <c r="F154" s="23" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G154" s="26" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H154" s="20">
         <v>301</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A155" s="16">
         <v>46303</v>
       </c>
@@ -4772,16 +4772,16 @@
         <v>15</v>
       </c>
       <c r="F155" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="G155" s="27" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="G155" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="H155" s="22">
         <v>301</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A156" s="16">
         <v>46303</v>
       </c>
@@ -4798,16 +4798,16 @@
         <v>18</v>
       </c>
       <c r="F156" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="G156" s="23" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="G156" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="H156" s="20">
         <v>301</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A157" s="16">
         <v>46303</v>
       </c>
@@ -4824,16 +4824,16 @@
         <v>21</v>
       </c>
       <c r="F157" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="G157" s="27" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="G157" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="H157" s="22">
         <v>301</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A158" s="16">
         <v>46304</v>
       </c>
@@ -4850,16 +4850,16 @@
         <v>12</v>
       </c>
       <c r="F158" s="23" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G158" s="26" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H158" s="20">
         <v>301</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A159" s="16">
         <v>46304</v>
       </c>
@@ -4876,16 +4876,16 @@
         <v>15</v>
       </c>
       <c r="F159" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="G159" s="27" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="G159" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="H159" s="22">
         <v>301</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A160" s="16">
         <v>46304</v>
       </c>
@@ -4902,10 +4902,10 @@
         <v>18</v>
       </c>
       <c r="F160" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="G160" s="23" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="G160" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="H160" s="20">
         <v>301</v>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFE3DE5-6A4C-47D6-9236-4E9FBEAC05E6}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8C488E-A869-49B4-AB1D-1BD577CEE1B8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" activeTab="2" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
     <sheet name="submission" sheetId="2" r:id="rId2"/>
+    <sheet name="staff" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="269">
   <si>
     <t>Date</t>
   </si>
@@ -184,13 +185,673 @@
   </si>
   <si>
     <t>Master Thesis</t>
+  </si>
+  <si>
+    <t>Sl.No</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. </t>
+  </si>
+  <si>
+    <t>Krishna Koppa</t>
+  </si>
+  <si>
+    <t>KK</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Aditya Deepak Talankar</t>
+  </si>
+  <si>
+    <t>ADT</t>
+  </si>
+  <si>
+    <t>Business Analytics</t>
+  </si>
+  <si>
+    <t>Ms.</t>
+  </si>
+  <si>
+    <t>Amita Kumari Gupta</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Avinash Rana</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Kavya Shabu</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>Naveen Kumar V</t>
+  </si>
+  <si>
+    <t>NKV</t>
+  </si>
+  <si>
+    <t>Praveen Gujjar</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>Shiksha Singhal</t>
+  </si>
+  <si>
+    <t>SSL</t>
+  </si>
+  <si>
+    <t>Syed Shahid Raza</t>
+  </si>
+  <si>
+    <t>SYR</t>
+  </si>
+  <si>
+    <t>Balaji Gopalan</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>Decision Science</t>
+  </si>
+  <si>
+    <t>Bharath Sampath</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>Jaykumar Padmanabhan</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>L Sudershan Reddy</t>
+  </si>
+  <si>
+    <t>LSR</t>
+  </si>
+  <si>
+    <t>Navaneetha Kumar V</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>Neeraj Kumar</t>
+  </si>
+  <si>
+    <t>Ravishankar S Ulle</t>
+  </si>
+  <si>
+    <t>RSU</t>
+  </si>
+  <si>
+    <t>Rupesh Kumar Sinha</t>
+  </si>
+  <si>
+    <t>RKS</t>
+  </si>
+  <si>
+    <t>Shashi Kant Dikshit</t>
+  </si>
+  <si>
+    <t>SKD</t>
+  </si>
+  <si>
+    <t>Thilak Reddy C</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vijaya G S </t>
+  </si>
+  <si>
+    <t>GSV</t>
+  </si>
+  <si>
+    <t>Vinoth Kumar V</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>Yavana Rani S</t>
+  </si>
+  <si>
+    <t>YR</t>
+  </si>
+  <si>
+    <t>Yogananthan S</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>Dr.</t>
+  </si>
+  <si>
+    <t>Udhayan N</t>
+  </si>
+  <si>
+    <t>UD</t>
+  </si>
+  <si>
+    <t>Bhavani M</t>
+  </si>
+  <si>
+    <t>Chinmaya Kumar Sahu</t>
+  </si>
+  <si>
+    <t>Gayatri Dwivedi</t>
+  </si>
+  <si>
+    <t>Thomas P K</t>
+  </si>
+  <si>
+    <t>PKT</t>
+  </si>
+  <si>
+    <t>Vijayalakshmi P</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>Anusha Shambuling Sangondimath</t>
+  </si>
+  <si>
+    <t>ANS</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Chaya Bagrecha</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>Deepika K M</t>
+  </si>
+  <si>
+    <t>DKM</t>
+  </si>
+  <si>
+    <t>Gnanendra M</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>Gopalakrishnan Chinnasamy</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>Hanish Kukreja</t>
+  </si>
+  <si>
+    <t>HKJ</t>
+  </si>
+  <si>
+    <t>Khushboo Tanwer</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>Kiran Kumar M</t>
+  </si>
+  <si>
+    <t>KKM</t>
+  </si>
+  <si>
+    <t>Manita D Shah</t>
+  </si>
+  <si>
+    <t>MDS</t>
+  </si>
+  <si>
+    <t>Mansi Kukreja</t>
+  </si>
+  <si>
+    <t>MK</t>
+  </si>
+  <si>
+    <t>Nagesh B</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>Premalatha K P</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>Pujari Sudharsana Reddy</t>
+  </si>
+  <si>
+    <t>PSR</t>
+  </si>
+  <si>
+    <t>Ramaprabha D</t>
+  </si>
+  <si>
+    <t>RP</t>
+  </si>
+  <si>
+    <t>Ravichandran K</t>
+  </si>
+  <si>
+    <t>RK</t>
+  </si>
+  <si>
+    <t>Renuka S</t>
+  </si>
+  <si>
+    <t>SRK</t>
+  </si>
+  <si>
+    <t>Selvi S</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Shrinivas Patil</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Sireesha Nanduri</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>Srinivasan Arun Kumar</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>Tarun Kashni</t>
+  </si>
+  <si>
+    <t>TK</t>
+  </si>
+  <si>
+    <t>Tejaswini S</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>V Y John</t>
+  </si>
+  <si>
+    <t>VYJ</t>
+  </si>
+  <si>
+    <t>Vedantam Seetha Ram</t>
+  </si>
+  <si>
+    <t>VSR</t>
+  </si>
+  <si>
+    <t>Vinoth S</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>Ishita Gopi</t>
+  </si>
+  <si>
+    <t>IG</t>
+  </si>
+  <si>
+    <t>General Management</t>
+  </si>
+  <si>
+    <t>M K Lodi</t>
+  </si>
+  <si>
+    <t>MKL</t>
+  </si>
+  <si>
+    <t>Ramneek Kalsang Bawa</t>
+  </si>
+  <si>
+    <t>RKB</t>
+  </si>
+  <si>
+    <t>Salma Begum</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>Santhosh C</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t>Sarangapani Nivarthi</t>
+  </si>
+  <si>
+    <t>SPN</t>
+  </si>
+  <si>
+    <t>Senthil Kumar B</t>
+  </si>
+  <si>
+    <t>SKB</t>
+  </si>
+  <si>
+    <t>Senthilkumar B</t>
+  </si>
+  <si>
+    <t>Shakeela Banu C</t>
+  </si>
+  <si>
+    <t>SBC</t>
+  </si>
+  <si>
+    <t>Shalu Singh</t>
+  </si>
+  <si>
+    <t>SHS</t>
+  </si>
+  <si>
+    <t>Srinivasan Pazhamalai</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>Sumangala Talur</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Syed Kazim</t>
+  </si>
+  <si>
+    <t>SYK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma C Swadimath </t>
+  </si>
+  <si>
+    <t>USM</t>
+  </si>
+  <si>
+    <t>Anantha Subramanya Iyer</t>
+  </si>
+  <si>
+    <t>ASI</t>
+  </si>
+  <si>
+    <t>Halaswamy D</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t>Hemanth Kumar S</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>Irum Khan</t>
+  </si>
+  <si>
+    <t>IK</t>
+  </si>
+  <si>
+    <t>Kalavathy K S</t>
+  </si>
+  <si>
+    <t>KKS</t>
+  </si>
+  <si>
+    <t>M Govindaraj</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>M H Sharieff</t>
+  </si>
+  <si>
+    <t>MHS</t>
+  </si>
+  <si>
+    <t>Madhavi Kappagantula</t>
+  </si>
+  <si>
+    <t>MVK</t>
+  </si>
+  <si>
+    <t>Mahalakshmi S</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Rahul Gupta</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>Saurabh Srivastava</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>Sharat Kumar</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>Smita M Gaikwad</t>
+  </si>
+  <si>
+    <t>Soney Haris</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>Sudarshan Venkataram Seshanna</t>
+  </si>
+  <si>
+    <t>SVS</t>
+  </si>
+  <si>
+    <t>Suparna Ghosal</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>Trupti Dandekar Humnekar</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>Umesh Chandra</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>Chetna</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>OB and HRM</t>
+  </si>
+  <si>
+    <t>Dinesh Neelakanta Rao</t>
+  </si>
+  <si>
+    <t>DN</t>
+  </si>
+  <si>
+    <t>Gayathri R</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>Nalini Sunil M</t>
+  </si>
+  <si>
+    <t>MNS</t>
+  </si>
+  <si>
+    <t>Neena P C</t>
+  </si>
+  <si>
+    <t>NPC</t>
+  </si>
+  <si>
+    <t>Pooja Nagpal</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>Satyajeet Nanda</t>
+  </si>
+  <si>
+    <t>SJN</t>
+  </si>
+  <si>
+    <t>Shivangi Gera</t>
+  </si>
+  <si>
+    <t>SHG</t>
+  </si>
+  <si>
+    <t>Vinayak Anil Bhat</t>
+  </si>
+  <si>
+    <t>VB</t>
+  </si>
+  <si>
+    <t>Aiswarya Babu N</t>
+  </si>
+  <si>
+    <t>ABN</t>
+  </si>
+  <si>
+    <t>SAAM</t>
+  </si>
+  <si>
+    <t>Karthik Kudkuli</t>
+  </si>
+  <si>
+    <t>KKG</t>
+  </si>
+  <si>
+    <t>Somasundaram G</t>
+  </si>
+  <si>
+    <t>SSG</t>
+  </si>
+  <si>
+    <t>Praveen Shaju</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>Ashwini R H</t>
+  </si>
+  <si>
+    <t>ARH</t>
+  </si>
+  <si>
+    <t>Jaya Bhavya K</t>
+  </si>
+  <si>
+    <t>JBK</t>
+  </si>
+  <si>
+    <t>Meenakshi Kumari</t>
+  </si>
+  <si>
+    <t>MKU</t>
+  </si>
+  <si>
+    <t>Dilip Gopalakrishna</t>
+  </si>
+  <si>
+    <t>DGO</t>
+  </si>
+  <si>
+    <t>Dorapudi Sri Harsha</t>
+  </si>
+  <si>
+    <t>SRH</t>
+  </si>
+  <si>
+    <t>Kiran Kumar N</t>
+  </si>
+  <si>
+    <t>KN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,8 +921,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,6 +978,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -335,10 +1009,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -422,11 +1097,72 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A164AA60-B9D2-4582-BAA8-0033E9D13E24}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5663,4 +6399,1835 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1909B0-CF20-4973-833D-034A4DF22C86}">
+  <dimension ref="A1:E106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A1" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A3" s="30">
+        <v>2</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A4" s="30">
+        <v>3</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A5" s="30">
+        <v>4</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A6" s="30">
+        <v>5</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A7" s="30">
+        <v>6</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A8" s="30">
+        <v>7</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A9" s="30">
+        <v>8</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A10" s="30">
+        <v>9</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A11" s="30">
+        <v>10</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A12" s="30">
+        <v>11</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A13" s="30">
+        <v>12</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A14" s="30">
+        <v>13</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A15" s="30">
+        <v>14</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A16" s="30">
+        <v>15</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A17" s="30">
+        <v>16</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="30">
+        <v>17</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A19" s="30">
+        <v>18</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A20" s="30">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A21" s="30">
+        <v>20</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A22" s="30">
+        <v>21</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A23" s="30">
+        <v>22</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A24" s="30">
+        <v>23</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="30">
+        <v>24</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A26" s="30">
+        <v>25</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A27" s="30">
+        <v>26</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A28" s="30">
+        <v>27</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A29" s="30">
+        <v>28</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A30" s="30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A31" s="30">
+        <v>30</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A32" s="30">
+        <v>31</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A33" s="30">
+        <v>32</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A34" s="30">
+        <v>33</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A35" s="30">
+        <v>34</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A36" s="30">
+        <v>35</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A37" s="30">
+        <v>36</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A38" s="30">
+        <v>37</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A39" s="30">
+        <v>38</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A40" s="30">
+        <v>39</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A41" s="30">
+        <v>40</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A42" s="30">
+        <v>41</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A43" s="30">
+        <v>42</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A44" s="30">
+        <v>43</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A45" s="30">
+        <v>44</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A46" s="30">
+        <v>45</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A47" s="30">
+        <v>46</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A48" s="30">
+        <v>47</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A49" s="30">
+        <v>48</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A50" s="30">
+        <v>49</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A51" s="30">
+        <v>50</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A52" s="30">
+        <v>51</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A53" s="30">
+        <v>52</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A54" s="30">
+        <v>53</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A55" s="30">
+        <v>54</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A56" s="30">
+        <v>55</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A57" s="30">
+        <v>56</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A58" s="30">
+        <v>57</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A59" s="30">
+        <v>58</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A60" s="30">
+        <v>59</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A61" s="30">
+        <v>60</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A62" s="30">
+        <v>61</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A63" s="30">
+        <v>62</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A64" s="30">
+        <v>63</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C64" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A65" s="30">
+        <v>64</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A66" s="30">
+        <v>65</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A67" s="30">
+        <v>66</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A68" s="30">
+        <v>67</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D68" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A69" s="30">
+        <v>68</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A70" s="30">
+        <v>69</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A71" s="30">
+        <v>70</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A72" s="30">
+        <v>71</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A73" s="30">
+        <v>72</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A74" s="30">
+        <v>73</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="D74" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A75" s="30">
+        <v>74</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A76" s="30">
+        <v>75</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D76" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A77" s="30">
+        <v>76</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="D77" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A78" s="30">
+        <v>77</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A79" s="30">
+        <v>78</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A80" s="30">
+        <v>79</v>
+      </c>
+      <c r="B80" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="D80" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A81" s="30">
+        <v>80</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A82" s="30">
+        <v>81</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="D82" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A83" s="30">
+        <v>82</v>
+      </c>
+      <c r="B83" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A84" s="30">
+        <v>83</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="D84" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A85" s="30">
+        <v>84</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A86" s="30">
+        <v>85</v>
+      </c>
+      <c r="B86" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A87" s="30">
+        <v>86</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A88" s="30">
+        <v>87</v>
+      </c>
+      <c r="B88" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C88" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A89" s="30">
+        <v>88</v>
+      </c>
+      <c r="B89" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="D89" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A90" s="30">
+        <v>89</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="D90" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A91" s="30">
+        <v>90</v>
+      </c>
+      <c r="B91" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A92" s="30">
+        <v>91</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="D92" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A93" s="30">
+        <v>92</v>
+      </c>
+      <c r="B93" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="D93" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A94" s="30">
+        <v>93</v>
+      </c>
+      <c r="B94" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="D94" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E94" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A95" s="30">
+        <v>94</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="D95" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E95" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A96" s="30">
+        <v>95</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="D96" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E96" s="30" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A97" s="30">
+        <v>96</v>
+      </c>
+      <c r="B97" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D97" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E97" s="30" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A98" s="30">
+        <v>97</v>
+      </c>
+      <c r="B98" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="D98" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E98" s="30" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A99" s="30">
+        <v>98</v>
+      </c>
+      <c r="B99" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C99" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="D99" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="E99" s="30" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A100" s="30">
+        <v>99</v>
+      </c>
+      <c r="B100" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="D100" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A101" s="30">
+        <v>100</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="D101" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A102" s="30">
+        <v>101</v>
+      </c>
+      <c r="B102" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="E102" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A103" s="30">
+        <v>102</v>
+      </c>
+      <c r="B103" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="D103" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A104" s="30">
+        <v>103</v>
+      </c>
+      <c r="B104" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="D104" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="E104" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A105" s="30">
+        <v>104</v>
+      </c>
+      <c r="B105" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E105" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="16" x14ac:dyDescent="0.35">
+      <c r="A106" s="30">
+        <v>105</v>
+      </c>
+      <c r="B106" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C24 C26:C100">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C101">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102:C103">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C104:C106">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D8C488E-A869-49B4-AB1D-1BD577CEE1B8}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F29B645-AEAE-4B1B-BA70-E7CE05C0715F}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" activeTab="2" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="275">
   <si>
     <t>Date</t>
   </si>
@@ -845,6 +845,24 @@
   </si>
   <si>
     <t>KN</t>
+  </si>
+  <si>
+    <t>OPM</t>
+  </si>
+  <si>
+    <t>SVF</t>
+  </si>
+  <si>
+    <t>CWW/AAL</t>
+  </si>
+  <si>
+    <t>Career Readiness</t>
+  </si>
+  <si>
+    <t>International Connect</t>
+  </si>
+  <si>
+    <t>Club Activity</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1106,12 +1124,85 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A164AA60-B9D2-4582-BAA8-0033E9D13E24}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1496,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B20C511-92BA-4145-A0DE-1431FC38FEF8}">
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I257"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -6293,7 +6384,1868 @@
         <v>301</v>
       </c>
     </row>
+    <row r="186" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A186" s="16">
+        <v>46317</v>
+      </c>
+      <c r="B186" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C186" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D186" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G186" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H186" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A187" s="16">
+        <v>46317</v>
+      </c>
+      <c r="B187" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C187" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G187" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H187" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A188" s="16">
+        <v>46317</v>
+      </c>
+      <c r="B188" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C188" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D188" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F188" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G188" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H188" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A189" s="16">
+        <v>46317</v>
+      </c>
+      <c r="B189" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C189" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D189" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F189" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G189" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H189" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A190" s="16">
+        <v>46318</v>
+      </c>
+      <c r="B190" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C190" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G190" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H190" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A191" s="16">
+        <v>46318</v>
+      </c>
+      <c r="B191" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C191" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D191" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F191" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G191" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H191" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A192" s="16">
+        <v>46318</v>
+      </c>
+      <c r="B192" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C192" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F192" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G192" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H192" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A193" s="16">
+        <v>46318</v>
+      </c>
+      <c r="B193" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C193" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F193" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="G193" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="H193" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A194" s="16">
+        <v>46319</v>
+      </c>
+      <c r="B194" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C194" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D194" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G194" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H194" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="48" x14ac:dyDescent="0.35">
+      <c r="A195" s="16">
+        <v>46319</v>
+      </c>
+      <c r="B195" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C195" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D195" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F195" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="G195" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H195" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A196" s="16">
+        <v>46319</v>
+      </c>
+      <c r="B196" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C196" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D196" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F196" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G196" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H196" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A197" s="16">
+        <v>46319</v>
+      </c>
+      <c r="B197" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C197" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F197" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G197" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H197" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A198" s="16">
+        <v>46322</v>
+      </c>
+      <c r="B198" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C198" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G198" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H198" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A199" s="16">
+        <v>46322</v>
+      </c>
+      <c r="B199" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C199" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D199" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F199" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G199" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H199" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A200" s="16">
+        <v>46322</v>
+      </c>
+      <c r="B200" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C200" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F200" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G200" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H200" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A201" s="16">
+        <v>46322</v>
+      </c>
+      <c r="B201" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C201" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F201" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="G201" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="H201" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A202" s="16">
+        <v>46323</v>
+      </c>
+      <c r="B202" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G202" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H202" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A203" s="16">
+        <v>46323</v>
+      </c>
+      <c r="B203" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C203" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D203" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F203" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G203" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H203" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A204" s="16">
+        <v>46323</v>
+      </c>
+      <c r="B204" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C204" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D204" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F204" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G204" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H204" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A205" s="16">
+        <v>46323</v>
+      </c>
+      <c r="B205" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C205" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D205" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F205" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G205" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H205" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A206" s="16">
+        <v>46324</v>
+      </c>
+      <c r="B206" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C206" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D206" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F206" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G206" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H206" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A207" s="16">
+        <v>46324</v>
+      </c>
+      <c r="B207" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C207" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D207" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F207" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G207" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H207" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A208" s="16">
+        <v>46324</v>
+      </c>
+      <c r="B208" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C208" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D208" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F208" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G208" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H208" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A209" s="16">
+        <v>46324</v>
+      </c>
+      <c r="B209" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C209" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D209" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F209" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G209" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H209" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A210" s="16">
+        <v>46325</v>
+      </c>
+      <c r="B210" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D210" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F210" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G210" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H210" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A211" s="16">
+        <v>46325</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F211" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G211" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H211" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A212" s="16">
+        <v>46325</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F212" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G212" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H212" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A213" s="16">
+        <v>46325</v>
+      </c>
+      <c r="B213" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F213" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G213" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H213" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A214" s="16">
+        <v>46326</v>
+      </c>
+      <c r="B214" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C214" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G214" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H214" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A215" s="16">
+        <v>46326</v>
+      </c>
+      <c r="B215" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C215" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F215" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G215" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H215" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A216" s="16">
+        <v>46326</v>
+      </c>
+      <c r="B216" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C216" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F216" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G216" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H216" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A217" s="16">
+        <v>46326</v>
+      </c>
+      <c r="B217" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C217" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F217" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G217" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H217" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A218" s="16">
+        <v>46328</v>
+      </c>
+      <c r="B218" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F218" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G218" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H218" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A219" s="16">
+        <v>46328</v>
+      </c>
+      <c r="B219" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C219" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D219" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F219" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G219" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H219" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A220" s="16">
+        <v>46328</v>
+      </c>
+      <c r="B220" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D220" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G220" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A221" s="16">
+        <v>46328</v>
+      </c>
+      <c r="B221" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C221" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D221" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F221" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="G221" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="H221" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A222" s="16">
+        <v>46329</v>
+      </c>
+      <c r="B222" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C222" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D222" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G222" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H222" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A223" s="16">
+        <v>46329</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C223" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D223" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F223" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G223" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H223" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A224" s="16">
+        <v>46329</v>
+      </c>
+      <c r="B224" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C224" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D224" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G224" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H224" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A225" s="16">
+        <v>46329</v>
+      </c>
+      <c r="B225" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C225" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D225" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F225" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G225" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H225" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A226" s="16">
+        <v>46330</v>
+      </c>
+      <c r="B226" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C226" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D226" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F226" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G226" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H226" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A227" s="16">
+        <v>46330</v>
+      </c>
+      <c r="B227" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C227" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D227" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F227" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G227" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H227" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A228" s="16">
+        <v>46330</v>
+      </c>
+      <c r="B228" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C228" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F228" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G228" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H228" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A229" s="16">
+        <v>46330</v>
+      </c>
+      <c r="B229" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C229" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D229" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F229" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G229" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H229" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A230" s="16">
+        <v>46337</v>
+      </c>
+      <c r="B230" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D230" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F230" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G230" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H230" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A231" s="16">
+        <v>46337</v>
+      </c>
+      <c r="B231" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C231" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F231" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G231" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H231" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A232" s="16">
+        <v>46337</v>
+      </c>
+      <c r="B232" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C232" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F232" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G232" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H232" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A233" s="16">
+        <v>46337</v>
+      </c>
+      <c r="B233" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C233" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F233" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G233" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H233" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A234" s="16">
+        <v>46338</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C234" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D234" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F234" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G234" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H234" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A235" s="16">
+        <v>46338</v>
+      </c>
+      <c r="B235" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F235" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G235" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H235" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+      <c r="A236" s="16">
+        <v>46338</v>
+      </c>
+      <c r="B236" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C236" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F236" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G236" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H236" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A237" s="16">
+        <v>46338</v>
+      </c>
+      <c r="B237" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D237" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F237" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G237" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H237" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A238" s="16">
+        <v>46339</v>
+      </c>
+      <c r="B238" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C238" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G238" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H238" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A239" s="16">
+        <v>46339</v>
+      </c>
+      <c r="B239" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C239" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D239" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E239" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F239" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G239" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H239" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A240" s="16">
+        <v>46339</v>
+      </c>
+      <c r="B240" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F240" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G240" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H240" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A241" s="16">
+        <v>46339</v>
+      </c>
+      <c r="B241" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F241" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G241" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H241" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A242" s="16">
+        <v>46340</v>
+      </c>
+      <c r="B242" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C242" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D242" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F242" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G242" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H242" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A243" s="16">
+        <v>46340</v>
+      </c>
+      <c r="B243" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C243" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D243" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F243" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="G243" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H243" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A244" s="16">
+        <v>46340</v>
+      </c>
+      <c r="B244" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D244" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F244" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G244" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H244" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A245" s="16">
+        <v>46340</v>
+      </c>
+      <c r="B245" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C245" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D245" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F245" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H245" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A246" s="16">
+        <v>46342</v>
+      </c>
+      <c r="B246" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D246" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G246" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H246" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="48" x14ac:dyDescent="0.35">
+      <c r="A247" s="16">
+        <v>46342</v>
+      </c>
+      <c r="B247" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D247" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F247" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="G247" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H247" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A248" s="16">
+        <v>46342</v>
+      </c>
+      <c r="B248" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C248" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D248" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E248" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F248" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G248" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H248" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A249" s="16">
+        <v>46342</v>
+      </c>
+      <c r="B249" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D249" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E249" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F249" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="G249" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="H249" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A250" s="16">
+        <v>46343</v>
+      </c>
+      <c r="B250" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C250" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D250" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" s="32"/>
+      <c r="G250" s="20"/>
+      <c r="H250" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A251" s="16">
+        <v>46343</v>
+      </c>
+      <c r="B251" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C251" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D251" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E251" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F251" s="27"/>
+      <c r="G251" s="22"/>
+      <c r="H251" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A252" s="16">
+        <v>46343</v>
+      </c>
+      <c r="B252" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C252" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D252" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E252" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F252" s="23"/>
+      <c r="G252" s="20"/>
+      <c r="H252" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A253" s="16">
+        <v>46343</v>
+      </c>
+      <c r="B253" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C253" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D253" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E253" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F253" s="22"/>
+      <c r="G253" s="22"/>
+      <c r="H253" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A254" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B254" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C254" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D254" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F254" s="32"/>
+      <c r="G254" s="20"/>
+      <c r="H254" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A255" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B255" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C255" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D255" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F255" s="27"/>
+      <c r="G255" s="22"/>
+      <c r="H255" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A256" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B256" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C256" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D256" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F256" s="23"/>
+      <c r="G256" s="20"/>
+      <c r="H256" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A257" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B257" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D257" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F257" s="22"/>
+      <c r="G257" s="22"/>
+      <c r="H257" s="22">
+        <v>301</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="H192">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H193">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H196">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H207">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H210">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H211">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H228">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8214,19 +10166,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C24 C26:C100">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C103">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104:C106">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F29B645-AEAE-4B1B-BA70-E7CE05C0715F}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316932F8-CB6D-4EA0-BBEF-85412B55BD5F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="5400" yWindow="710" windowWidth="19200" windowHeight="10510" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="277">
   <si>
     <t>Date</t>
   </si>
@@ -863,6 +863,12 @@
   </si>
   <si>
     <t>Club Activity</t>
+  </si>
+  <si>
+    <t>1:15 - 2:46</t>
+  </si>
+  <si>
+    <t>1:15 - 2:47</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B20C511-92BA-4145-A0DE-1431FC38FEF8}">
-  <dimension ref="A1:I257"/>
+  <dimension ref="A1:I260"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -7528,12 +7534,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A230" s="16">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="B230" s="17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C230" s="17" t="s">
         <v>10</v>
@@ -7541,25 +7547,25 @@
       <c r="D230" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E230" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F230" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="G230" s="20" t="s">
-        <v>78</v>
+      <c r="E230" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F230" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G230" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="H230" s="20">
         <v>301</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A231" s="16">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C231" s="17" t="s">
         <v>10</v>
@@ -7568,24 +7574,24 @@
         <v>11</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F231" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="G231" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H231" s="22">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+      <c r="F231" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G231" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H231" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A232" s="16">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C232" s="17" t="s">
         <v>10</v>
@@ -7594,15 +7600,15 @@
         <v>11</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="F232" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="G232" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="H232" s="20">
+        <v>30</v>
+      </c>
+      <c r="G232" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H232" s="22">
         <v>301</v>
       </c>
     </row>
@@ -7619,25 +7625,25 @@
       <c r="D233" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E233" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F233" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="G233" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="H233" s="22">
+      <c r="E233" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G233" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H233" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A234" s="16">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C234" s="17" t="s">
         <v>10</v>
@@ -7645,25 +7651,25 @@
       <c r="D234" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E234" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F234" s="32" t="s">
+      <c r="E234" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F234" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="G234" s="20" t="s">
+      <c r="G234" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="H234" s="20">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="H234" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A235" s="16">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C235" s="17" t="s">
         <v>10</v>
@@ -7672,24 +7678,24 @@
         <v>11</v>
       </c>
       <c r="E235" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F235" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="G235" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H235" s="22">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" ht="32" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="F235" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G235" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H235" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A236" s="16">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C236" s="17" t="s">
         <v>10</v>
@@ -7698,15 +7704,15 @@
         <v>11</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F236" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F236" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="G236" s="20" t="s">
+      <c r="G236" s="22" t="s">
         <v>271</v>
       </c>
-      <c r="H236" s="20">
+      <c r="H236" s="22">
         <v>301</v>
       </c>
     </row>
@@ -7723,25 +7729,25 @@
       <c r="D237" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E237" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F237" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="G237" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="H237" s="22">
+      <c r="E237" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F237" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G237" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H237" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A238" s="16">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C238" s="17" t="s">
         <v>10</v>
@@ -7749,25 +7755,25 @@
       <c r="D238" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E238" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F238" s="32" t="s">
+      <c r="E238" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F238" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="G238" s="20" t="s">
+      <c r="G238" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H238" s="20">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="H238" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="32" x14ac:dyDescent="0.35">
       <c r="A239" s="16">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C239" s="17" t="s">
         <v>10</v>
@@ -7776,24 +7782,24 @@
         <v>11</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F239" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="G239" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H239" s="22">
+        <v>18</v>
+      </c>
+      <c r="F239" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G239" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H239" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A240" s="16">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C240" s="17" t="s">
         <v>10</v>
@@ -7802,15 +7808,15 @@
         <v>11</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F240" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="G240" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H240" s="20">
+        <v>21</v>
+      </c>
+      <c r="F240" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="G240" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="H240" s="22">
         <v>301</v>
       </c>
     </row>
@@ -7827,25 +7833,25 @@
       <c r="D241" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E241" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F241" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="G241" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H241" s="22">
+      <c r="E241" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G241" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H241" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A242" s="16">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C242" s="17" t="s">
         <v>10</v>
@@ -7853,25 +7859,25 @@
       <c r="D242" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E242" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F242" s="32" t="s">
+      <c r="E242" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F242" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="G242" s="20" t="s">
+      <c r="G242" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="H242" s="20">
+      <c r="H242" s="22">
         <v>301</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A243" s="16">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C243" s="17" t="s">
         <v>10</v>
@@ -7880,24 +7886,24 @@
         <v>11</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F243" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F243" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="G243" s="22" t="s">
+      <c r="G243" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H243" s="22">
+      <c r="H243" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A244" s="16">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>10</v>
@@ -7906,15 +7912,15 @@
         <v>11</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F244" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G244" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H244" s="20">
+        <v>21</v>
+      </c>
+      <c r="F244" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="G244" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H244" s="22">
         <v>301</v>
       </c>
     </row>
@@ -7931,25 +7937,25 @@
       <c r="D245" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E245" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F245" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G245" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="H245" s="22">
+      <c r="E245" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G245" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H245" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A246" s="16">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C246" s="17" t="s">
         <v>10</v>
@@ -7957,25 +7963,25 @@
       <c r="D246" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E246" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F246" s="32" t="s">
+      <c r="E246" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F246" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="G246" s="20" t="s">
+      <c r="G246" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H246" s="20">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" ht="48" x14ac:dyDescent="0.35">
+      <c r="H246" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A247" s="16">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C247" s="17" t="s">
         <v>10</v>
@@ -7984,24 +7990,24 @@
         <v>11</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F247" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="G247" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="H247" s="22">
+        <v>18</v>
+      </c>
+      <c r="F247" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G247" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H247" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A248" s="16">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B248" s="17" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C248" s="17" t="s">
         <v>10</v>
@@ -8010,15 +8016,15 @@
         <v>11</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F248" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="G248" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H248" s="20">
+        <v>21</v>
+      </c>
+      <c r="F248" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G248" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H248" s="22">
         <v>301</v>
       </c>
     </row>
@@ -8035,25 +8041,25 @@
       <c r="D249" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E249" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F249" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="G249" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="H249" s="22">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="E249" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F249" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G249" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H249" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="48" x14ac:dyDescent="0.35">
       <c r="A250" s="16">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B250" s="17" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C250" s="17" t="s">
         <v>10</v>
@@ -8061,21 +8067,25 @@
       <c r="D250" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E250" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F250" s="32"/>
-      <c r="G250" s="20"/>
-      <c r="H250" s="20">
+      <c r="E250" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F250" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="G250" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H250" s="22">
         <v>301</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A251" s="16">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C251" s="17" t="s">
         <v>10</v>
@@ -8084,20 +8094,24 @@
         <v>11</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F251" s="27"/>
-      <c r="G251" s="22"/>
-      <c r="H251" s="22">
+        <v>18</v>
+      </c>
+      <c r="F251" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G251" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H251" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A252" s="16">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B252" s="17" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C252" s="17" t="s">
         <v>10</v>
@@ -8106,11 +8120,15 @@
         <v>11</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F252" s="23"/>
-      <c r="G252" s="20"/>
-      <c r="H252" s="20">
+        <v>21</v>
+      </c>
+      <c r="F252" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="G252" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="H252" s="22">
         <v>301</v>
       </c>
     </row>
@@ -8127,21 +8145,21 @@
       <c r="D253" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E253" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F253" s="22"/>
-      <c r="G253" s="22"/>
-      <c r="H253" s="22">
+      <c r="E253" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F253" s="32"/>
+      <c r="G253" s="20"/>
+      <c r="H253" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A254" s="16">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C254" s="17" t="s">
         <v>10</v>
@@ -8149,21 +8167,21 @@
       <c r="D254" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E254" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F254" s="32"/>
-      <c r="G254" s="20"/>
-      <c r="H254" s="20">
+      <c r="E254" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F254" s="27"/>
+      <c r="G254" s="22"/>
+      <c r="H254" s="22">
         <v>301</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A255" s="16">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C255" s="17" t="s">
         <v>10</v>
@@ -8172,20 +8190,20 @@
         <v>11</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F255" s="27"/>
-      <c r="G255" s="22"/>
-      <c r="H255" s="22">
+        <v>18</v>
+      </c>
+      <c r="F255" s="23"/>
+      <c r="G255" s="20"/>
+      <c r="H255" s="20">
         <v>301</v>
       </c>
     </row>
     <row r="256" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A256" s="16">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C256" s="17" t="s">
         <v>10</v>
@@ -8194,11 +8212,11 @@
         <v>11</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F256" s="23"/>
-      <c r="G256" s="20"/>
-      <c r="H256" s="20">
+        <v>21</v>
+      </c>
+      <c r="F256" s="22"/>
+      <c r="G256" s="22"/>
+      <c r="H256" s="22">
         <v>301</v>
       </c>
     </row>
@@ -8215,36 +8233,103 @@
       <c r="D257" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E257" s="21" t="s">
+      <c r="E257" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F257" s="32"/>
+      <c r="G257" s="20"/>
+      <c r="H257" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A258" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B258" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C258" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D258" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F258" s="27"/>
+      <c r="G258" s="22"/>
+      <c r="H258" s="22">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A259" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B259" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C259" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D259" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F259" s="23"/>
+      <c r="G259" s="20"/>
+      <c r="H259" s="20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A260" s="16">
+        <v>46344</v>
+      </c>
+      <c r="B260" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C260" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D260" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E260" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F257" s="22"/>
-      <c r="G257" s="22"/>
-      <c r="H257" s="22">
+      <c r="F260" s="22"/>
+      <c r="G260" s="22"/>
+      <c r="H260" s="22">
         <v>301</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="H192">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H193">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H196">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H207">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H210">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H211">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H228">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="H228 H231">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10166,19 +10251,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C24 C26:C100">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102:C103">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104:C106">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316932F8-CB6D-4EA0-BBEF-85412B55BD5F}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A15F07A-AB1E-4426-8B0F-67B3FC8EF9F8}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="710" windowWidth="19200" windowHeight="10510" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -7582,7 +7582,7 @@
       <c r="G231" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="H231" s="20">
+      <c r="H231" s="22">
         <v>301</v>
       </c>
     </row>
@@ -8328,9 +8328,6 @@
   <conditionalFormatting sqref="H211">
     <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H228 H231">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
